--- a/output/2026-09-19_22_Croazia_Sibensko-kninska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-19_22_Croazia_Sibensko-kninska_Impiantistica_aspirazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Installa impianti di ventilazione anche per complessi industriali, ventilatori industriali/assiali/centrifughi. Confermato su sito ufficiale, tvrtke.hr, mojkvart.hr.</t>
+          <t>Installa impianti di ventilazione anche per complessi industriali, ventilatori industriali/assiali/centrifughi. Confermato su sito ufficiale, tvrtke.hr, mojkvart.hr. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,8 +536,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Installatore ventilazione/climatizzazione/riscaldamento/idraulici dal 2018. Nessuna menzione esplicita 'industriale' ma coerente come installatore generico. Confermato su sito e emajstor.hr.</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Impiantistica elettrotecnica/meccanica, ~15 dipendenti, sistemi di ventilazione classica/combinata. Confermato su sito, fininfo.hr, tvrtke.hr, companywall.hr. Sito attuale mostra anche sede/contatti alternativi (Ivana Meštrovića 13, 022 215 400) da riconfermare.</t>
+          <t>Impiantistica elettrotecnica/meccanica, ~15 dipendenti, sistemi di ventilazione classica/combinata. Confermato su sito, fininfo.hr, tvrtke.hr, companywall.hr. Sito attuale mostra anche sede/contatti alternativi (Ivana Meštrovića 13, 022 215 400) da riconfermare. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -639,7 +637,6 @@
           <t>Adria-Impex d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Šibensko-kninska (Šibenik)</t>
@@ -662,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ventilazione/climatizzazione/refrigerazione ~20 anni, anche in ambienti industriali/magazzini. Confermato su emajstor.hr, tvrtke.hr, kompass.com. Una fonte riporta telefono alternativo (022 216 241) vs quello fornito.</t>
+          <t>Ventilazione/climatizzazione/refrigerazione ~20 anni, anche in ambienti industriali/magazzini. Confermato su emajstor.hr, tvrtke.hr, kompass.com. Una fonte riporta telefono alternativo (022 216 241) vs quello fornito. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -725,7 +722,6 @@
           <t>Elpoh d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Šibensko-kninska (Šibenik)</t>

--- a/output/2026-09-19_22_Croazia_Sibensko-kninska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-19_22_Croazia_Sibensko-kninska_Impiantistica_aspirazione_industriale.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climatizzazione/refrigerazione/ventilazione residenziale-commerciale-industriale, dealer Daikin. Confermato su sito, daikin.hr, emajstor.hr.</t>
+          <t>Climatizzazione/refrigerazione/ventilazione residenziale-commerciale-industriale, dealer Daikin. Confermato su sito, daikin.hr, emajstor.hr. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
